--- a/artfynd/A 54741-2023 artfynd.xlsx
+++ b/artfynd/A 54741-2023 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115163312</v>
+        <v>115163310</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647272</v>
+        <v>647170</v>
       </c>
       <c r="R2" t="n">
-        <v>7100815</v>
+        <v>7100820</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,16 +785,11 @@
         <v>115163311</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -899,19 +889,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115163310</v>
+        <v>115163312</v>
       </c>
       <c r="B4" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>647170</v>
+        <v>647272</v>
       </c>
       <c r="R4" t="n">
-        <v>7100820</v>
+        <v>7100815</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,16 +999,11 @@
         <v>115163313</v>
       </c>
       <c r="B5" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">

--- a/artfynd/A 54741-2023 artfynd.xlsx
+++ b/artfynd/A 54741-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115163310</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115163311</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115163312</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,8 +1120,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115163313</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>